--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_ANTLERLESS_PRIVATE_LANDS_ONLY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_ELK_ANTLERLESS_PRIVATE_LANDS_ONLY.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -531,6 +531,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -584,10 +585,15 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -645,7 +651,8 @@
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -703,7 +710,8 @@
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>9.2</t>
         </is>
@@ -761,7 +769,8 @@
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -818,8 +827,13 @@
           <t>53.5</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
@@ -876,8 +890,13 @@
           <t>46.7</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -934,8 +953,13 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -992,8 +1016,13 @@
           <t>27.8</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -1050,8 +1079,13 @@
           <t>26.2</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
@@ -1108,8 +1142,13 @@
           <t>41.6</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>9.7</t>
         </is>
@@ -1166,8 +1205,13 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -1224,8 +1268,13 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -1282,8 +1331,13 @@
           <t>40.9</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -1340,8 +1394,13 @@
           <t>25</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
@@ -1398,8 +1457,13 @@
           <t>36.7</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
@@ -1456,8 +1520,13 @@
           <t>60</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -1514,8 +1583,13 @@
           <t>48.1</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
@@ -1572,8 +1646,13 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
@@ -1631,7 +1710,8 @@
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -1688,8 +1768,13 @@
           <t>21.4</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
@@ -1747,7 +1832,8 @@
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -1805,7 +1891,8 @@
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
@@ -1862,8 +1949,13 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -1920,8 +2012,13 @@
           <t>34.7</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>7.2</t>
         </is>
@@ -1978,8 +2075,13 @@
           <t>53.7</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -2036,8 +2138,13 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
@@ -2095,7 +2202,8 @@
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="6" t="inlineStr">
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>7.4</t>
         </is>
@@ -2153,7 +2261,8 @@
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
